--- a/astro-site/public/dl/guia-restaurante-mexicano/cash-flow-break-even.xlsx
+++ b/astro-site/public/dl/guia-restaurante-mexicano/cash-flow-break-even.xlsx
@@ -11,7 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Break-Even" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Cash Flow'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -517,9 +519,9 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -539,6 +541,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -567,10 +570,19 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Celdas verdes = campos editables</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/guia-restaurante-mexicano · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -579,7 +591,16 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -588,7 +609,7 @@
   <sheetPr>
     <tabColor rgb="00009688"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -622,6 +643,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1114,6 +1136,7 @@
       <c r="L27" s="8" t="n"/>
       <c r="M27" s="8" t="n"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
@@ -1127,7 +1150,16 @@
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1136,7 +1168,7 @@
   <sheetPr>
     <tabColor rgb="00FF5722"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1159,6 +1191,8 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
@@ -1209,6 +1243,7 @@
         <v>39100</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
@@ -1217,7 +1252,7 @@
       </c>
       <c r="B11" s="13">
         <f>B5*B6*B7</f>
-        <v/>
+        <v>53040.0</v>
       </c>
     </row>
     <row r="12">
@@ -1227,8 +1262,8 @@
         </is>
       </c>
       <c r="B12" s="13">
-        <f>B12*(1-B8)</f>
-        <v/>
+        <f>B11*(1-B8)</f>
+        <v>36597.6</v>
       </c>
     </row>
     <row r="13">
@@ -1238,6 +1273,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
@@ -1251,6 +1287,15 @@
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>